--- a/output/pdf_financials_xlsx/AEG.xlsx
+++ b/output/pdf_financials_xlsx/AEG.xlsx
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.067</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.061</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1636,7 +1636,7 @@
         </is>
       </c>
       <c r="O20" s="3" t="n">
-        <v>-4.707</v>
+        <v>1.482</v>
       </c>
       <c r="P20" s="3" t="n">
         <v>1.482</v>
@@ -2040,10 +2040,10 @@
         <v>9.186999999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.887</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-8.753</v>
+        <v>-8.692</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-7.638</v>
@@ -2162,10 +2162,10 @@
         <v>9.186999999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.279</v>
+        <v>9.346</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.302</v>
+        <v>-8.241</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-7.136</v>
@@ -2223,10 +2223,10 @@
         <v>36.49835127726352</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>37.11451541938322</v>
+        <v>37.38250469981201</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-31.5114248842329</v>
+        <v>-31.27989068549305</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-26.24687362071502</v>
@@ -7429,22 +7429,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-2.653</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-1.696</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>30</v>
+        <v>29.948</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>-1.006</v>
+        <v>-1.206</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>-2.403</v>
+        <v>-0.203</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.096</v>
       </c>
     </row>
     <row r="125">
@@ -7484,22 +7484,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-2.653</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-1.696</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>60</v>
+        <v>59.948</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>-1.006</v>
+        <v>-1.206</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>-2.403</v>
+        <v>-0.203</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.096</v>
       </c>
     </row>
     <row r="126">
@@ -29700,7 +29700,11 @@
           <t>Lease payments (Note 15)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -33432,7 +33436,11 @@
           <t>Lease payments (Note 16)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -36008,7 +36016,11 @@
           <t>Lease payments (Note 17)</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -38524,7 +38536,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E324" t="inlineStr">
         <is>
           <t>-</t>
@@ -54030,7 +54046,11 @@
           <t>Net income, continuing operations - - - -</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -68878,7 +68898,7 @@
       </c>
       <c r="D644" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E644" t="inlineStr">
@@ -68976,7 +68996,7 @@
       </c>
       <c r="D645" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E645" t="inlineStr">
@@ -69074,7 +69094,7 @@
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E646" t="inlineStr">

--- a/output/pdf_financials_xlsx/AEG.xlsx
+++ b/output/pdf_financials_xlsx/AEG.xlsx
@@ -2104,10 +2104,10 @@
         <v>0.392</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.451</v>
+        <v>1.167</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.502</v>
+        <v>1.251</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>1.272</v>
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.02</v>
+        <v>1.071</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.02</v>
+        <v>1.068</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.02</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="29">
@@ -2165,10 +2165,10 @@
         <v>9.346</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-8.241</v>
+        <v>-7.525</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.136</v>
+        <v>-6.387</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-30.103</v>
@@ -2201,13 +2201,13 @@
         </is>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.261</v>
+        <v>-1.21</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.469</v>
+        <v>3.517</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>8.839</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="30">
@@ -2226,10 +2226,10 @@
         <v>37.38250469981201</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-31.27989068549305</v>
+        <v>-28.56221058225157</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-26.24687362071502</v>
+        <v>-23.49198175665735</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-106.8543234417152</v>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-7.448756571563589</v>
+        <v>-7.147498375568551</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>19.36582370345559</v>
+        <v>19.63378551889689</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>51.08362711668497</v>
+        <v>51.43616713864648</v>
       </c>
     </row>
     <row r="31">
@@ -6085,46 +6085,46 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.392</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>1.251</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.272</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.465</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>1.474</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>1.335</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>1.215</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>1.071</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>1.068</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="101">
@@ -6739,16 +6739,16 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.295</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.049</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -27824,7 +27824,11 @@
           <t>Depreciation of property and equipment (Note 11)</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -28010,7 +28014,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -32110,7 +32114,11 @@
           <t>Depreciation of property and equipment (Note 12)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -32300,7 +32308,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -34002,7 +34010,11 @@
           <t>Depreciation of property and equipment (Note 13)</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -34192,7 +34204,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -36670,7 +36682,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -36754,7 +36770,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -46188,7 +46204,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -46852,7 +46868,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E412" s="5" t="n">
         <v>0.076</v>
       </c>
@@ -47598,7 +47618,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>0.333</v>
       </c>
@@ -50146,7 +50170,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -50332,7 +50360,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
